--- a/evidence-templates/B4.2_DecisionLog_CFS_v1.xlsx
+++ b/evidence-templates/B4.2_DecisionLog_CFS_v1.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Deploy Azure Firewall Standard SKU (not Premium) for lab</t>
+          <t>Deploy Azure Firewall Premium SKU with IDPS (Deny) for lab</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Standard SKU covers all lab scenarios (L4 network rules, L7 app rules, FQDN filtering). Premium adds TLS inspection and IDPS — valuable for production but increases lab cost by ~60%. NVAs excluded (require licenses).</t>
+          <t>Premium SKU enables IDPS in Deny mode for PSD2 Art. 95 network anomaly detection, required by the CFS fintech scenario. Standard rejected: no IDPS. TLS inspection is a documented design-only upgrade (needs customer CA). NVAs excluded (require licenses).</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Cost: ~€3/hour saving vs Premium. Risk: Missing IDPS testing — documented as known gap. Schedule: No impact.</t>
+          <t>Cost: ~€3/hour higher than Standard. Risk: low for lab — IDPS Deny only blocks signature-matched exploits, not benign traffic. Schedule: Premium provisioning adds a few minutes.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Azure Front Door Standard (not Premium or CDN Classic) for global HTTP/S delivery</t>
+          <t>Azure Front Door Premium (Private Link origin to App Gateway) for global HTTP/S delivery</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>AFD Standard provides global anycast, WAF, and health routing sufficient for lab. Premium adds Private Link origin (useful for production, adds cost). CDN Classic is being retired. Traffic Manager is DNS-only — no TLS termination or WAF.</t>
+          <t>AFD Premium provides a Private Link origin to the App Gateway so the origin is never publicly exposed (CFS Zero-Trust requirement), plus a managed WAF (DRS 2.1 + Bot Manager). Standard rejected: public origin only. CDN Classic is retiring. Traffic Manager is DNS-only (no TLS/WAF).</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Cost: AFD Standard ~€0.01/GB + fixed monthly. Risk: AFD Premium Private Link origin not demonstrated — documented gap. Schedule: No impact.</t>
+          <t>Cost: AFD Premium fixed monthly + ~€0.01/GB. Risk: the origin Private Link request must be approved post-deploy (automated by the deploy scripts/workflow). Schedule: No impact.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
